--- a/worksheet.xlsx
+++ b/worksheet.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -739,26 +739,64 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>KNOWN LIMITATION: convert_worksheet.py currently reads 'Elective Groups'/'Elective Options'</t>
+          <t>AUTOMATIC CROSS-CCC GAP CHECK: every time you run build_dist.py, it automatically checks every</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>for your own reference but does NOT yet feed pick-N-of-M logic into the app -- the app's</t>
+          <t>required-but-unarticulated course at every CCC against every OTHER CCC's catalog -- if another</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>data model only understands flat 'required' lists right now. The data is captured here so</t>
+          <t>CCC in your dataset offers it, it's reported on the console and written to</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>dist/cross_ccc_alternatives.json. This runs on every future addition too, not just today's data --</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>no need to check for this by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>KNOWN LIMITATION: convert_worksheet.py currently reads 'Elective Groups'/'Elective Options'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>for your own reference but does NOT yet feed pick-N-of-M logic into the app -- the app's</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>data model only understands flat 'required' lists right now. The data is captured here so</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>it isn't lost, ready for whenever the app/frontend is extended to actually display choices.</t>
         </is>
@@ -955,7 +993,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>CONFIRMED via actual UCSD ASSIST agreements (both De Anza and EVC PDFs agree). Official 'General Advice' list: MATH 20A/20B/20C (calc1/2/3), MATH 20D (diffeq), MATH 18 (linalg), calc-based physics series (physics1/2/3), CSE 8B-or-11 (prog1), CSE 12 (prog2), CSE 20 (discrete). CORRECTION from an earlier version of this sheet: discrete math IS explicitly required (previously left unmarked); Computer Organization is NOT in the official required list (previously marked required in error) -- it appears in the detailed per-CCC table but not the summary bullet list, so treat it as unconfirmed.</t>
+          <t>CONFIRMED via actual UCSD ASSIST agreements (both De Anza and EVC PDFs agree). Official 'General Advice' list: MATH 20A/20B/20C (calc1/2/3), MATH 20D (diffeq), MATH 18 (linalg), calc-based physics series (physics1/2/3), CSE 8B-or-11 (prog1), CSE 12 (prog2), CSE 20 (discrete). CSE 30 (comporg) is ALSO required -- user confirmed via the live page after this sheet initially left it out because it wasn't in the summary bullet list (only in the detailed per-CCC table). Lesson: the detailed table is the authoritative source; the prose summary isn't necessarily exhaustive.</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
@@ -998,7 +1036,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N2" s="9" t="n"/>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="O2" s="9" t="n"/>
       <c r="P2" s="8" t="inlineStr">
         <is>
@@ -1023,7 +1065,7 @@
       <c r="X2" s="9" t="n"/>
       <c r="Y2" s="10" t="inlineStr">
         <is>
-          <t>Fully confirmed row -- see source note. Computer Organization intentionally left blank (not in official required list).</t>
+          <t>Fully confirmed row, including comporg (CSE 30) -- confirmed against the live page after this sheet initially missed it.</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1284,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H3 H5 I5 J3 J5 K3 K4 K5 L3 L5 M3 M4 M5 N2 N3 N4 N5 O2 O3 O4 O5 P3 P5 Q3 Q5 R3 R5 S2 S3 S5 T2 T3 T4 T5 U2 U3 U4 U5 V2 V3 V4 W2 W3 W4 W5 X2 X4 X5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3 H5 I5 J3 J5 K3 K4 K5 L3 L5 M3 M4 M5 N3 N4 N5 O2 O3 O4 O5 P3 P5 Q3 Q5 R3 R5 S2 S3 S5 T2 T3 T4 T5 U2 U3 U4 U5 V2 V3 V4 W2 W3 W4 W5 X2 X4 X5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"X,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1473,12 +1515,12 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>COMSC 075 (or CIT 044 Java)</t>
+          <t>CIT 044 (or COMSC 076) for UCSD; CIT 044 (or COMSC 075) for UCI -- differs by receiving school, see limitation note</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>CONFIRMED via actual ASSIST agreement PDFs (2025-2026, this session).</t>
+          <t>SEE LIMITATION NOTE: EVC's prog1 course also differs by receiving school (COMSC 076 for UCSD, COMSC 075 for UCI, both alongside CIT 044) -- same one-cell-per-slot limitation as calc3.</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1540,10 @@
           <t>CIS 22C (or 22CH)</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>COMSC 076</t>
-        </is>
-      </c>
+      <c r="D9" s="9" t="n"/>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>CONFIRMED via actual ASSIST agreement PDFs (2025-2026, this session).</t>
+          <t>GAP AT EVC for UCSD Computer Engineering: CSE 12 has no EVC equivalent (confirmed against the live ASSIST page). Students can instead complete it via De Anza College's CIS 22C (or 22CH) -- confirmed on De Anza's own agreement -- by cross-enrolling or taking it there before transfer. This is exactly the kind of gap dist/cross_ccc_alternatives.json now finds automatically on every build.</t>
         </is>
       </c>
     </row>
@@ -1520,9 +1558,21 @@
           <t>Computer Organization</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="12" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>CIS 21JA + CIS 21JB + CIS 26B (or CIS 26BH honors) -- inferred by structural parallel with EVC's same 'Complete A or B' section; not read as clearly as EVC's mapping was</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>COMSC 077 (Introduction to Computer Systems)</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>CONFIRMED via actual ASSIST agreement PDFs (2025-2026, this session).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1700,9 +1750,21 @@
           <t>Introduction to Psychology</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="12" t="n"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>PSYC C1000 + PSYC 24 for COGS 9A; PSYC C1000 + (PSYC 4 or PSYC 8) for COGS 9C -- differs by which COGS course it satisfies, same limitation pattern as calc3</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>PSYC C1000 + PSYCH 030 for COGS 9A; PSYC C1000 + PSYCH 099 for COGS 9C -- differs by which COGS course it satisfies, same limitation pattern as calc3</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>SEE LIMITATION NOTE: this slot needs a different course combo depending on whether it's satisfying UCI's COGS 9A or COGS 9C -- same one-cell-per-slot limitation as calc3 and prog1.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">

--- a/worksheet.xlsx
+++ b/worksheet.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCC Catalog" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elective Groups" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elective Options" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slot Reference" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AP Credit" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slot Reference" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -777,26 +778,57 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>KNOWN LIMITATION: convert_worksheet.py currently reads 'Elective Groups'/'Elective Options'</t>
+          <t>AP CREDIT: the 'AP Credit' tab lists which AP exam + minimum score satisfies which slot, sourced</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>for your own reference but does NOT yet feed pick-N-of-M logic into the app -- the app's</t>
+          <t>from official UC AP credit charts (not guessed). build_dist.py turns this into dist/ap_credit.json,</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>data model only understands flat 'required' lists right now. The data is captured here so</t>
+          <t>which the frontend can check against a student's uploaded scores. Add more rows here (AP CS A,</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>AP Physics C, etc.) the same way -- one row per (school, exam, min score, slot).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>KNOWN LIMITATION: convert_worksheet.py currently reads 'Elective Groups'/'Elective Options'</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>for your own reference but does NOT yet feed pick-N-of-M logic into the app -- the app's</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>data model only understands flat 'required' lists right now. The data is captured here so</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>it isn't lost, ready for whenever the app/frontend is extended to actually display choices.</t>
         </is>
@@ -2003,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2152,12 +2184,12 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>physics_2course</t>
+          <t>physics_calc_based</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>EVC PHYS 007A + PHYS 007B (only 2 courses -- EVC has no 3rd physics course option here)</t>
+          <t>EVC PHYS 007A + PHYS 007B (only 2 courses -- EVC has no 3rd course here). This satisfies UCI's CALCULUS-BASED 'Classical Physics' sequence (PHYSICS 7C/7D/7E) specifically.</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -2174,12 +2206,12 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>physics_2course</t>
+          <t>physics_calc_based</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>EVC PHYS 007A + PHYS 007B (only 2 courses -- EVC has no 3rd physics course option here)</t>
+          <t>EVC PHYS 007A + PHYS 007B (only 2 courses -- EVC has no 3rd course here). This satisfies UCI's CALCULUS-BASED 'Classical Physics' sequence (PHYSICS 7C/7D/7E) specifically.</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -2196,19 +2228,15 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>statistics</t>
+          <t>physics_algebra_based</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>EVC STAT C1000 (or BUS 060)</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>stats_gen</t>
-        </is>
-      </c>
+          <t>UCI ALSO separately accepts an ALGEBRA-based 'Basic Physics' sequence (PHYSICS 3A/3B/3C) as an alternative option -- this is NOT the same course sequence as physics1/2/3 above and is NOT interchangeable with it (confirmed: user verified these are non-equivalent). No EVC course has been confirmed against this specific algebra-based track -- do not assume the calc-based mapping above covers it.</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2218,15 +2246,19 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>logic</t>
+          <t>statistics</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>EVC PHIL 090 (Introduction to Logic) -- no matching slot tracked here</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr"/>
+          <t>EVC STAT C1000 (or BUS 060)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>stats_gen</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2236,12 +2268,12 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>linguistics</t>
+          <t>logic</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>No EVC equivalent exists for any linguistics option (LSCI 3/10/20/51)</t>
+          <t>EVC PHIL 090 (Introduction to Logic) -- no matching slot tracked here</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr"/>
@@ -2254,12 +2286,12 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>neuro_electives</t>
+          <t>linguistics</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>No EVC equivalent exists for extra neuro electives (BIO SCI 36/37/38)</t>
+          <t>No EVC equivalent exists for any linguistics option (LSCI 3/10/20/51)</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr"/>
@@ -2267,24 +2299,20 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>uci_cogsci_electives_deanza</t>
+          <t>uci_cogsci_electives_evc</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>programming</t>
+          <t>neuro_electives</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Programming series: De Anza CIS 40 + CIS 41A + CIS 41B (3 courses)</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>prog1</t>
-        </is>
-      </c>
+          <t>No EVC equivalent exists for extra neuro electives (BIO SCI 36/37/38)</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -2304,7 +2332,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>prog2</t>
+          <t>prog1</t>
         </is>
       </c>
     </row>
@@ -2316,15 +2344,19 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>linguistics</t>
+          <t>programming</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>De Anza LING 1 (Introduction to Linguistics) -- real equivalent, unlike EVC</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr"/>
+          <t>Programming series: De Anza CIS 40 + CIS 41A + CIS 41B (3 courses)</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>prog2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -2334,12 +2366,12 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>logic</t>
+          <t>linguistics</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>De Anza PHIL 7 (Deductive Logic, or 7H honors) -- real equivalent, unlike EVC</t>
+          <t>De Anza LING 1 (Introduction to Linguistics) -- real equivalent, unlike EVC</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr"/>
@@ -2352,19 +2384,15 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>multivar_calc</t>
+          <t>logic</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>De Anza MATH 1D (Calculus IV) -- satisfies UCI's MATH 2D/2E multivariable pair</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>calc3</t>
-        </is>
-      </c>
+          <t>De Anza PHIL 7 (Deductive Logic, or 7H honors) -- real equivalent, unlike EVC</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -2374,17 +2402,17 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>linear_algebra</t>
+          <t>multivar_calc</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>De Anza MATH 2B (or 2BH)</t>
+          <t>De Anza MATH 1D (Calculus IV) -- satisfies UCI's MATH 2D/2E multivariable pair</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>linalg</t>
+          <t>calc3</t>
         </is>
       </c>
     </row>
@@ -2396,17 +2424,17 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>diffeq</t>
+          <t>linear_algebra</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>De Anza MATH 2A (or 2AH) -- note De Anza's OWN numbering: their 'MATH 2A' means Diff Eq, not Calc I</t>
+          <t>De Anza MATH 2B (or 2BH)</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>diffeq</t>
+          <t>linalg</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2446,17 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>physics_3course</t>
+          <t>diffeq</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>De Anza PHYS 2A/2B/2C (5 units, DEPRECATED next fall) OR PHYS 4A/4B/4C (6 units, use this one going forward)</t>
+          <t>De Anza MATH 2A (or 2AH) -- note De Anza's OWN numbering: their 'MATH 2A' means Diff Eq, not Calc I</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>physics1</t>
+          <t>diffeq</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2468,17 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>physics_3course</t>
+          <t>physics_calc_based</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>De Anza PHYS 2A/2B/2C (5 units, DEPRECATED next fall) OR PHYS 4A/4B/4C (6 units, use this one going forward)</t>
+          <t>De Anza PHYS 2A/2B/2C (5 units, DEPRECATED next fall) OR PHYS 4A/4B/4C (6 units, use this one going forward). This satisfies UCI's CALCULUS-BASED 'Classical Physics' sequence (PHYSICS 7C/7D/7E) specifically.</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>physics2</t>
+          <t>physics1</t>
         </is>
       </c>
     </row>
@@ -2462,17 +2490,17 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>physics_3course</t>
+          <t>physics_calc_based</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>De Anza PHYS 2A/2B/2C (5 units, DEPRECATED next fall) OR PHYS 4A/4B/4C (6 units, use this one going forward)</t>
+          <t>De Anza PHYS 2A/2B/2C (5 units, DEPRECATED next fall) OR PHYS 4A/4B/4C (6 units, use this one going forward). This satisfies UCI's CALCULUS-BASED 'Classical Physics' sequence (PHYSICS 7C/7D/7E) specifically.</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>physics3</t>
+          <t>physics2</t>
         </is>
       </c>
     </row>
@@ -2484,68 +2512,64 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>statistics</t>
+          <t>physics_calc_based</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>De Anza STAT C1000 (or Honors), or PSYC 15 / POLI 20 (same as SOC 15)</t>
+          <t>De Anza PHYS 2A/2B/2C (5 units, DEPRECATED next fall) OR PHYS 4A/4B/4C (6 units, use this one going forward). This satisfies UCI's CALCULUS-BASED 'Classical Physics' sequence (PHYSICS 7C/7D/7E) specifically.</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>stats_gen</t>
+          <t>physics3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>ucsd_cogsci_electives_evc</t>
+          <t>uci_cogsci_electives_deanza</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>neuro</t>
+          <t>physics_algebra_based</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>EVC PSYCH 030 (Intro Biological Psychology) -- likely satisfies a neuro-focused option</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>neuro_intro</t>
-        </is>
-      </c>
+          <t>UCI ALSO separately accepts an ALGEBRA-based 'Basic Physics' sequence (PHYSICS 3A/3B/3C) as an alternative option -- this is NOT the same course sequence as physics1/2/3 above and is NOT interchangeable with it (confirmed: user verified these are non-equivalent). No De Anza course has been confirmed against this specific algebra-based track -- do not assume the calc-based mapping above covers it.</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>ucsd_cogsci_electives_evc</t>
+          <t>uci_cogsci_electives_deanza</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>programming</t>
+          <t>statistics</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>EVC COMSC 075, or CIT 044 (Java) + COMSC 076 combo -- ambiguous exact UCSD target course</t>
+          <t>De Anza STAT C1000 (or Honors), or PSYC 15 / POLI 20 (same as SOC 15)</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>prog1</t>
+          <t>stats_gen</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>ucsd_cogsci_electives_deanza</t>
+          <t>ucsd_cogsci_electives_evc</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -2555,7 +2579,7 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>De Anza PSYC 24 (Introduction to Psychobiology) -- likely satisfies COGS 17 Neurobiology of Cognition</t>
+          <t>EVC PSYCH 030 (Intro Biological Psychology) -- likely satisfies a neuro-focused option</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
@@ -2567,36 +2591,68 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
+          <t>ucsd_cogsci_electives_evc</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>programming</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>EVC COMSC 075, or CIT 044 (Java) + COMSC 076 combo -- ambiguous exact UCSD target course</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>prog1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
           <t>ucsd_cogsci_electives_deanza</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>neuro</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>De Anza PSYC 24 (Introduction to Psychobiology) -- likely satisfies COGS 17 Neurobiology of Cognition</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>neuro_intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>ucsd_cogsci_electives_deanza</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>programming</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>De Anza: mostly 'No Course Articulated' for the COGS18/CSE6R/CSE8A/CSE11-style intro Python options; CIS 40 Python + CIS 41A, or CIS 35A/36B Java, may partially apply -- needs your visual check of the actual table</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>prog1</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="n"/>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="15" t="n"/>
-      <c r="D29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="n"/>
@@ -2634,9 +2690,21 @@
       <c r="C35" s="15" t="n"/>
       <c r="D35" s="15" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D28 D29 D30 D31 D32 D33 D34 D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D30 D31 D32 D33 D34 D35 D36 D37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"calc1,calc2,calc3,linalg,diffeq,discrete,prog1,prog2,comporg,digital_logic,physics1,physics2,physics3,circuits,stats_gen,linguistics,psych_intro,neuro_intro,cogsci_research,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2645,6 +2713,246 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>school_key</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>AP Exam</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Minimum Score</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>slot_id</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>ucsd</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Calculus AB</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>calc1</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>Exempts MATH 20A. AB score of 3 only exempts MATH 10A, a different sequence -- not counted as satisfying calc1 here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>ucsd</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Calculus BC</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>calc1</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Exempts MATH 20A (per official UC chart: 'exempt Mathematics 20A or 10A,10B').</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>ucsd</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Calculus BC</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>calc2</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Score of 4 or 5 exempts MATH 20A AND 20B. A BC score of 3 alone is NOT enough for calc2 -- only counted here at 4+.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>uci</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Calculus AB</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>calc1</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Any passing AB score (3, 4, or 5) exempts MATH 2A per UCI's official AP credit chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>uci</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Calculus BC</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>calc1</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Exempts MATH 2A (places into MATH 2B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>uci</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Calculus BC</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>calc2</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Score of 4 or 5 exempts MATH 2A AND 2B. A BC score of 3 alone only exempts 2A, not 2B -- only counted here at 4+.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
